--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/CONNECTICUT_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/CONNECTICUT_2019.xlsx
@@ -1435,7 +1435,7 @@
         <v>28</v>
       </c>
       <c r="D60">
-        <v>0.009641873278236915</v>
+        <v>0.009641873278236917</v>
       </c>
     </row>
     <row r="61">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C132">
@@ -5701,7 +5701,7 @@
         <v>28</v>
       </c>
       <c r="D297">
-        <v>0.009641873278236915</v>
+        <v>0.009641873278236917</v>
       </c>
     </row>
     <row r="298">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C355">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C375">
@@ -9157,7 +9157,7 @@
         <v>28</v>
       </c>
       <c r="D489">
-        <v>0.009641873278236915</v>
+        <v>0.009641873278236917</v>
       </c>
     </row>
     <row r="490">
@@ -9373,7 +9373,7 @@
         <v>28</v>
       </c>
       <c r="D501">
-        <v>0.009641873278236915</v>
+        <v>0.009641873278236917</v>
       </c>
     </row>
     <row r="502">
@@ -9787,7 +9787,7 @@
         <v>28</v>
       </c>
       <c r="D524">
-        <v>0.009641873278236915</v>
+        <v>0.009641873278236917</v>
       </c>
     </row>
     <row r="525">
